--- a/library/transformers.xlsx
+++ b/library/transformers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA7B645-7FFA-4649-8722-EDA864B42E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC4838A-1C9C-5E46-97B6-B9A9D2E51C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="transformers" sheetId="5" r:id="rId1"/>
@@ -316,6 +316,8 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="21">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{5A4A247A-9E13-45F7-8C42-156984DFCA88}"/>
     <cellStyle name="Accent 1 1" xfId="3" xr:uid="{59C07D72-8E19-46CF-887A-3117F6F3785F}"/>
     <cellStyle name="Accent 2 1" xfId="4" xr:uid="{6BABBE6D-B89F-40A5-B377-65A1ECF4F8D6}"/>
     <cellStyle name="Accent 3 1" xfId="5" xr:uid="{4C06F33B-F628-495C-9BA2-60FAC1B8690A}"/>
@@ -335,8 +337,6 @@
     <cellStyle name="Status 1" xfId="17" xr:uid="{B5CEB193-82F1-4869-9033-6CA5CF994AD1}"/>
     <cellStyle name="Text 1" xfId="18" xr:uid="{82FD0F21-4428-49B3-91A7-88A1E12D7A17}"/>
     <cellStyle name="Warning 1" xfId="19" xr:uid="{C0F92B33-BA6B-43EB-9AF1-3DB4037EF412}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="2" xr:uid="{5A4A247A-9E13-45F7-8C42-156984DFCA88}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -352,9 +352,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -392,7 +392,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -498,7 +498,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -640,7 +640,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -649,17 +649,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D7E81C-1413-426F-8EBE-717C09928723}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="7" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="7" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -682,7 +679,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -702,7 +699,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -722,7 +719,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -742,7 +739,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -762,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -782,7 +779,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -802,7 +799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
